--- a/reports/excel/MacroPulse_2026-06-04.xlsx
+++ b/reports/excel/MacroPulse_2026-06-04.xlsx
@@ -651,7 +651,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2.15e+05</t>
+          <t>2.25e+05</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1.786e+06</t>
+          <t>1.777e+06</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>-4.54%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🔥 通膨指標　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>🔥 通膨指標　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>📈 經濟成長　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>📈 經濟成長　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -24692,7 +24692,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>👷 勞動市場　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>👷 勞動市場　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -24833,7 +24833,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>2.33e+05</t>
+          <t>2.38e+05</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -24878,12 +24878,12 @@
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K4" s="19" t="inlineStr">
         <is>
-          <t>1.862e+06</t>
+          <t>1.853e+06</t>
         </is>
       </c>
       <c r="L4" s="19" t="inlineStr">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="M4" s="19" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="N4" s="19" t="inlineStr">
@@ -24930,42 +24930,42 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>157,748</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>+0.700 pp</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>2.38e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -24975,12 +24975,12 @@
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
         <is>
-          <t>1.853e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -24990,79 +24990,79 @@
       </c>
       <c r="M5" s="20" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,426</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-14.22%</t>
         </is>
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>157,748</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>+0.700 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.23e+05</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -25072,12 +25072,12 @@
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-6.30%</t>
         </is>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.864e+06</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">
@@ -25087,44 +25087,44 @@
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>7,426</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
         <is>
-          <t>-14.22%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>2.23e+05</t>
+          <t>2.41e+05</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -25169,12 +25169,12 @@
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>-6.30%</t>
+          <t>8.07%</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>1.864e+06</t>
+          <t>1.848e+06</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -25184,7 +25184,7 @@
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -25221,7 +25221,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>2.41e+05</t>
+          <t>2.37e+05</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>1.848e+06</t>
+          <t>1.873e+06</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
@@ -25318,7 +25318,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -25353,7 +25353,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>2.37e+05</t>
+          <t>2.48e+05</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -25363,12 +25363,12 @@
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
-          <t>1.873e+06</t>
+          <t>1.871e+06</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="M9" s="20" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -25415,42 +25415,42 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>157,757</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>+0.500 pp</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>2.48e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -25460,12 +25460,12 @@
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
-          <t>1.871e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" s="19" t="inlineStr">
@@ -25475,79 +25475,79 @@
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.22</t>
         </is>
       </c>
       <c r="O10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,520</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-18.74%</t>
         </is>
       </c>
       <c r="S10" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>157,757</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>+0.500 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.34e+05</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -25557,12 +25557,12 @@
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-5.64%</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.863e+06</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -25572,44 +25572,44 @@
       </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>35.22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
-          <t>7,520</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R11" s="20" t="inlineStr">
         <is>
-          <t>-18.74%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>2.34e+05</t>
+          <t>2.28e+05</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
@@ -25654,12 +25654,12 @@
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>-5.64%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>1.863e+06</t>
+          <t>1.855e+06</t>
         </is>
       </c>
       <c r="L12" s="19" t="inlineStr">
@@ -25706,7 +25706,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>2.28e+05</t>
+          <t>2.32e+05</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -25751,12 +25751,12 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>1.855e+06</t>
+          <t>1.862e+06</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -25803,7 +25803,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
@@ -25848,22 +25848,22 @@
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K14" s="19" t="inlineStr">
         <is>
-          <t>1.862e+06</t>
+          <t>1.847e+06</t>
         </is>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="M14" s="19" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="N14" s="19" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -25935,32 +25935,32 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>2.32e+05</t>
+          <t>2.27e+05</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>-5.42%</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>1.847e+06</t>
+          <t>1.845e+06</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -25997,201 +25997,201 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>157,912</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>2.27e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>-5.42%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
-          <t>1.845e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="P16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,943</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-25.01%</t>
         </is>
       </c>
       <c r="S16" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-7.67%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>157,912</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.27e+05</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.825e+06</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr">
         <is>
-          <t>6,943</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R17" s="20" t="inlineStr">
         <is>
-          <t>-25.01%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr">
         <is>
-          <t>-7.67%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
@@ -26226,32 +26226,32 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>2.27e+05</t>
+          <t>2.23e+05</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-4.29%</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
-          <t>1.825e+06</t>
+          <t>1.831e+06</t>
         </is>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
@@ -26288,7 +26288,7 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -26323,32 +26323,32 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>2.23e+05</t>
+          <t>2.21e+05</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>-4.29%</t>
+          <t>-7.14%</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
-          <t>1.831e+06</t>
+          <t>1.825e+06</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -26385,7 +26385,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -26420,32 +26420,32 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>2.21e+05</t>
+          <t>2.27e+05</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>1.825e+06</t>
+          <t>1.858e+06</t>
         </is>
       </c>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="N20" s="19" t="inlineStr">
@@ -26482,201 +26482,201 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>157,945</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>2.27e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
-          <t>1.858e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="Q21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,379</t>
         </is>
       </c>
       <c r="R21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-14.00%</t>
         </is>
       </c>
       <c r="S21" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.28%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>157,945</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.58e+05</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7.05%</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>13.66%</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.869e+06</t>
         </is>
       </c>
       <c r="L22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>7,379</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>-14.00%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S22" s="19" t="inlineStr">
         <is>
-          <t>6.28%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -26711,32 +26711,32 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>2.58e+05</t>
+          <t>2.41e+05</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>7.05%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>13.66%</t>
+          <t>-6.59%</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>1.869e+06</t>
+          <t>1.882e+06</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -26773,7 +26773,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -26808,32 +26808,32 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>2.41e+05</t>
+          <t>2.27e+05</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>-8.47%</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>-6.59%</t>
+          <t>-5.81%</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
-          <t>1.882e+06</t>
+          <t>1.853e+06</t>
         </is>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -26905,32 +26905,32 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>2.27e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>-8.47%</t>
+          <t>-6.41%</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>-5.81%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>1.853e+06</t>
+          <t>1.876e+06</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -26967,201 +26967,201 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,079</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>+0.500 pp</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>-6.41%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>1.876e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" s="19" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="19" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="P26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,566</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-12.04%</t>
         </is>
       </c>
       <c r="S26" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>158,079</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>+0.500 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.21e+05</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.87e+06</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="20" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P27" s="20" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q27" s="20" t="inlineStr">
         <is>
-          <t>7,566</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R27" s="20" t="inlineStr">
         <is>
-          <t>-12.04%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S27" s="20" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -27196,32 +27196,32 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>2.21e+05</t>
+          <t>2.18e+05</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
+        <is>
+          <t>1.887e+06</t>
+        </is>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="inlineStr">
+        <is>
           <t>0.91%</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>1.87e+06</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>0.81%</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
@@ -27258,7 +27258,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -27293,17 +27293,17 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>2.18e+05</t>
+          <t>2.16e+05</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>-6.90%</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -27313,12 +27313,12 @@
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -27355,7 +27355,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -27390,32 +27390,32 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>2.16e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>-6.90%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K30" s="19" t="inlineStr">
         <is>
-          <t>1.887e+06</t>
+          <t>1.866e+06</t>
         </is>
       </c>
       <c r="L30" s="19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="M30" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="N30" s="19" t="inlineStr">
@@ -27452,7 +27452,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -27487,32 +27487,32 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>2.22e+05</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
         <is>
-          <t>1.866e+06</t>
+          <t>1.859e+06</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -27549,201 +27549,201 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,316</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>-2.20%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J32" s="19" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K32" s="19" t="inlineStr">
         <is>
-          <t>1.859e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L32" s="19" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M32" s="19" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,295</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-14.38%</t>
         </is>
       </c>
       <c r="S32" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.58%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>158,316</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>0.15%</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.38e+05</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.73%</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.865e+06</t>
         </is>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
-          <t>7,295</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R33" s="20" t="inlineStr">
         <is>
-          <t>-14.38%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S33" s="20" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -27778,32 +27778,32 @@
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>2.38e+05</t>
+          <t>2.22e+05</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>6.73%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>-6.72%</t>
         </is>
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>1.865e+06</t>
+          <t>1.881e+06</t>
         </is>
       </c>
       <c r="L34" s="19" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="M34" s="19" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="N34" s="19" t="inlineStr">
@@ -27840,7 +27840,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -27875,32 +27875,32 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
         <is>
-          <t>-6.72%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="K35" s="20" t="inlineStr">
         <is>
-          <t>1.881e+06</t>
+          <t>1.833e+06</t>
         </is>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="M35" s="20" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -27937,7 +27937,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -27972,32 +27972,32 @@
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>2.12e+05</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-17.83%</t>
         </is>
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="K36" s="19" t="inlineStr">
         <is>
-          <t>1.833e+06</t>
+          <t>1.868e+06</t>
         </is>
       </c>
       <c r="L36" s="19" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
@@ -28034,201 +28034,201 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,268</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>2.12e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>-17.83%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
         <is>
-          <t>-3.20%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>1.868e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="20" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="P37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,431</t>
         </is>
       </c>
       <c r="R37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-11.30%</t>
         </is>
       </c>
       <c r="S37" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>158,268</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.06e+05</t>
         </is>
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-14.52%</t>
         </is>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="K38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.85e+06</t>
         </is>
       </c>
       <c r="L38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P38" s="19" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>7,431</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>-11.30%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S38" s="19" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -28263,32 +28263,32 @@
       </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
-          <t>2.06e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>-14.52%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
         <is>
-          <t>-2.83%</t>
+          <t>6.31%</t>
         </is>
       </c>
       <c r="K39" s="20" t="inlineStr">
         <is>
-          <t>1.85e+06</t>
+          <t>1.891e+06</t>
         </is>
       </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
@@ -28325,7 +28325,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>2025-01-11</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -28360,32 +28360,32 @@
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>2.23e+05</t>
         </is>
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
-          <t>1.891e+06</t>
+          <t>1.854e+06</t>
         </is>
       </c>
       <c r="L40" s="19" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="N40" s="19" t="inlineStr">
@@ -28422,7 +28422,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -28457,32 +28457,32 @@
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>2.23e+05</t>
+          <t>2.12e+05</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="K41" s="20" t="inlineStr">
         <is>
-          <t>1.854e+06</t>
+          <t>1.876e+06</t>
         </is>
       </c>
       <c r="L41" s="20" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="M41" s="20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -28519,201 +28519,201 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,310</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>2.12e+05</t>
+          <t>2.2e+05</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K42" s="19" t="inlineStr">
         <is>
-          <t>1.876e+06</t>
+          <t>1.84e+06</t>
         </is>
       </c>
       <c r="L42" s="19" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="M42" s="19" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,242</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-14.19%</t>
         </is>
       </c>
       <c r="S42" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.54%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>158,310</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>2.2e+05</t>
+          <t>2.16e+05</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="K43" s="20" t="inlineStr">
         <is>
-          <t>1.84e+06</t>
+          <t>1.862e+06</t>
         </is>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="M43" s="20" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O43" s="20" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P43" s="20" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
-          <t>7,242</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R43" s="20" t="inlineStr">
         <is>
-          <t>-14.19%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S43" s="20" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -28748,32 +28748,32 @@
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>2.16e+05</t>
+          <t>2.23e+05</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>1.862e+06</t>
+          <t>1.849e+06</t>
         </is>
       </c>
       <c r="L44" s="19" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
@@ -28810,7 +28810,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -28845,32 +28845,32 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>2.23e+05</t>
+          <t>2.41e+05</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>8.07%</t>
         </is>
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
-          <t>1.849e+06</t>
+          <t>1.889e+06</t>
         </is>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="M45" s="20" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -28907,201 +28907,201 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,377</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>2.41e+05</t>
+          <t>2.24e+05</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr">
         <is>
-          <t>8.56%</t>
+          <t>-5.88%</t>
         </is>
       </c>
       <c r="J46" s="19" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>-7.05%</t>
         </is>
       </c>
       <c r="K46" s="19" t="inlineStr">
         <is>
-          <t>1.889e+06</t>
+          <t>1.857e+06</t>
         </is>
       </c>
       <c r="L46" s="19" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="P46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,952</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-15.28%</t>
         </is>
       </c>
       <c r="S46" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.00%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>158,377</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G47" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
-          <t>2.24e+05</t>
+          <t>2.22e+05</t>
         </is>
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>-5.88%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J47" s="20" t="inlineStr">
         <is>
-          <t>-7.05%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="K47" s="20" t="inlineStr">
         <is>
-          <t>1.857e+06</t>
+          <t>1.876e+06</t>
         </is>
       </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M47" s="20" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P47" s="20" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q47" s="20" t="inlineStr">
         <is>
-          <t>6,952</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R47" s="20" t="inlineStr">
         <is>
-          <t>-15.28%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S47" s="20" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
@@ -29136,32 +29136,32 @@
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>2.25e+05</t>
         </is>
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>1.876e+06</t>
+          <t>1.852e+06</t>
         </is>
       </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="N48" s="19" t="inlineStr">
@@ -29198,7 +29198,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -29233,32 +29233,32 @@
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>2.25e+05</t>
+          <t>2.24e+05</t>
         </is>
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="J49" s="20" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="K49" s="20" t="inlineStr">
         <is>
-          <t>1.852e+06</t>
+          <t>1.889e+06</t>
         </is>
       </c>
       <c r="L49" s="20" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="M49" s="20" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="N49" s="20" t="inlineStr">
@@ -29295,7 +29295,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -29330,32 +29330,32 @@
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>2.24e+05</t>
+          <t>2.2e+05</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>1.889e+06</t>
+          <t>1.852e+06</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
@@ -29392,201 +29392,201 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,485</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>2.2e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J51" s="20" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K51" s="20" t="inlineStr">
         <is>
-          <t>1.852e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L51" s="20" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M51" s="20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.12</t>
         </is>
       </c>
       <c r="O51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="P51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="Q51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,098</t>
         </is>
       </c>
       <c r="R51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-5.72%</t>
         </is>
       </c>
       <c r="S51" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>158,485</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.23e+05</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="J52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.876e+06</t>
         </is>
       </c>
       <c r="L52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="19" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P52" s="19" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>7,098</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>-5.72%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S52" s="19" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -29621,32 +29621,32 @@
       </c>
       <c r="H53" s="20" t="inlineStr">
         <is>
-          <t>2.23e+05</t>
+          <t>2.17e+05</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="J53" s="20" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="K53" s="20" t="inlineStr">
         <is>
-          <t>1.876e+06</t>
+          <t>1.84e+06</t>
         </is>
       </c>
       <c r="L53" s="20" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
@@ -29683,7 +29683,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
@@ -29718,32 +29718,32 @@
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>2.17e+05</t>
+          <t>2.24e+05</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K54" s="19" t="inlineStr">
         <is>
-          <t>1.84e+06</t>
+          <t>1.906e+06</t>
         </is>
       </c>
       <c r="L54" s="19" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="M54" s="19" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr">
@@ -29780,7 +29780,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
@@ -29815,32 +29815,32 @@
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>2.24e+05</t>
+          <t>2.39e+05</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>8.64%</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>6.70%</t>
         </is>
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
-          <t>1.906e+06</t>
+          <t>1.876e+06</t>
         </is>
       </c>
       <c r="L55" s="20" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="M55" s="20" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="N55" s="20" t="inlineStr">
@@ -29877,201 +29877,201 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,498</t>
         </is>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>2.39e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr">
         <is>
-          <t>8.64%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J56" s="19" t="inlineStr">
         <is>
-          <t>6.70%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K56" s="19" t="inlineStr">
         <is>
-          <t>1.876e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L56" s="19" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M56" s="19" t="inlineStr">
         <is>
-          <t>-1.57%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.28</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="P56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,310</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-6.07%</t>
         </is>
       </c>
       <c r="S56" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>158,498</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.28e+05</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="J57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.884e+06</t>
         </is>
       </c>
       <c r="L57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="M57" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O57" s="20" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P57" s="20" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
-          <t>7,310</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R57" s="20" t="inlineStr">
         <is>
-          <t>-6.07%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S57" s="20" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -30106,32 +30106,32 @@
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>2.28e+05</t>
+          <t>2.26e+05</t>
         </is>
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>-4.60%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="K58" s="19" t="inlineStr">
         <is>
-          <t>1.884e+06</t>
+          <t>1.889e+06</t>
         </is>
       </c>
       <c r="L58" s="19" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="M58" s="19" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="N58" s="19" t="inlineStr">
@@ -30168,7 +30168,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
@@ -30203,32 +30203,32 @@
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>2.26e+05</t>
+          <t>2.25e+05</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>-6.64%</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>1.889e+06</t>
+          <t>1.917e+06</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="M59" s="20" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
@@ -30265,7 +30265,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -30300,32 +30300,32 @@
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
-          <t>2.25e+05</t>
+          <t>2.36e+05</t>
         </is>
       </c>
       <c r="I60" s="19" t="inlineStr">
         <is>
-          <t>-6.64%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="J60" s="19" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="K60" s="19" t="inlineStr">
         <is>
-          <t>1.917e+06</t>
+          <t>1.896e+06</t>
         </is>
       </c>
       <c r="L60" s="19" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="M60" s="19" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="N60" s="19" t="inlineStr">
@@ -30362,7 +30362,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -30397,32 +30397,32 @@
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>2.36e+05</t>
+          <t>2.44e+05</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K61" s="20" t="inlineStr">
         <is>
-          <t>1.896e+06</t>
+          <t>1.947e+06</t>
         </is>
       </c>
       <c r="L61" s="20" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="M61" s="20" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="N61" s="20" t="inlineStr">
@@ -30459,201 +30459,201 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,478</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F62" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="G62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.200 pp</t>
         </is>
       </c>
       <c r="H62" s="19" t="inlineStr">
         <is>
-          <t>2.44e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I62" s="19" t="inlineStr">
         <is>
-          <t>9.91%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J62" s="19" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K62" s="19" t="inlineStr">
         <is>
-          <t>1.947e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L62" s="19" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M62" s="19" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="O62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="P62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="Q62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,204</t>
         </is>
       </c>
       <c r="R62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="S62" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.45%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>158,478</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G63" s="20" t="inlineStr">
         <is>
-          <t>-0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.46e+05</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9.33%</t>
         </is>
       </c>
       <c r="J63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.935e+06</t>
         </is>
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="M63" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O63" s="20" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P63" s="20" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q63" s="20" t="inlineStr">
         <is>
-          <t>7,204</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R63" s="20" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S63" s="20" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
@@ -30688,32 +30688,32 @@
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>2.46e+05</t>
+          <t>2.43e+05</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>8.48%</t>
         </is>
       </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="K64" s="19" t="inlineStr">
         <is>
-          <t>1.935e+06</t>
+          <t>1.96e+06</t>
         </is>
       </c>
       <c r="L64" s="19" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
@@ -30750,7 +30750,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
@@ -30785,32 +30785,32 @@
       </c>
       <c r="H65" s="20" t="inlineStr">
         <is>
-          <t>2.43e+05</t>
+          <t>2.36e+05</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>8.48%</t>
+          <t>7.27%</t>
         </is>
       </c>
       <c r="J65" s="20" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
-          <t>1.96e+06</t>
+          <t>1.954e+06</t>
         </is>
       </c>
       <c r="L65" s="20" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="M65" s="20" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
@@ -30847,7 +30847,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -30882,32 +30882,32 @@
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>2.36e+05</t>
+          <t>2.31e+05</t>
         </is>
       </c>
       <c r="I66" s="19" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="J66" s="19" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="K66" s="19" t="inlineStr">
         <is>
-          <t>1.954e+06</t>
+          <t>1.952e+06</t>
         </is>
       </c>
       <c r="L66" s="19" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="M66" s="19" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="N66" s="19" t="inlineStr">
@@ -30944,201 +30944,201 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,542</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E67" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>2.31e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K67" s="20" t="inlineStr">
         <is>
-          <t>1.952e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L67" s="20" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M67" s="20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="O67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="P67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,089</t>
         </is>
       </c>
       <c r="R67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.54%</t>
         </is>
       </c>
       <c r="S67" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.60%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>158,542</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.28e+05</t>
         </is>
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.07%</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="K68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.949e+06</t>
         </is>
       </c>
       <c r="L68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="M68" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O68" s="19" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P68" s="19" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q68" s="19" t="inlineStr">
         <is>
-          <t>7,089</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R68" s="19" t="inlineStr">
         <is>
-          <t>-4.54%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S68" s="19" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
@@ -31173,32 +31173,32 @@
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>2.28e+05</t>
+          <t>2.21e+05</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="K69" s="20" t="inlineStr">
         <is>
-          <t>1.949e+06</t>
+          <t>1.941e+06</t>
         </is>
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="M69" s="20" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -31235,7 +31235,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
@@ -31270,32 +31270,32 @@
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>2.21e+05</t>
+          <t>2.18e+05</t>
         </is>
       </c>
       <c r="I70" s="19" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-8.79%</t>
         </is>
       </c>
       <c r="J70" s="19" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="K70" s="19" t="inlineStr">
         <is>
-          <t>1.941e+06</t>
+          <t>1.936e+06</t>
         </is>
       </c>
       <c r="L70" s="19" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="M70" s="19" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="N70" s="19" t="inlineStr">
@@ -31332,7 +31332,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
@@ -31367,32 +31367,32 @@
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>2.18e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>-8.79%</t>
+          <t>-3.95%</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K71" s="20" t="inlineStr">
         <is>
-          <t>1.936e+06</t>
+          <t>1.963e+06</t>
         </is>
       </c>
       <c r="L71" s="20" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="M71" s="20" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="N71" s="20" t="inlineStr">
@@ -31429,201 +31429,201 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,472</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E72" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F72" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I72" s="19" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J72" s="19" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K72" s="19" t="inlineStr">
         <is>
-          <t>1.963e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" s="19" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" s="19" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="O72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="P72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="Q72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,919</t>
         </is>
       </c>
       <c r="R72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-7.99%</t>
         </is>
       </c>
       <c r="S72" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.40%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="22" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>158,472</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.26e+05</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.942e+06</t>
         </is>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="M73" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.07%</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O73" s="20" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P73" s="20" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q73" s="20" t="inlineStr">
         <is>
-          <t>6,919</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R73" s="20" t="inlineStr">
         <is>
-          <t>-7.99%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S73" s="20" t="inlineStr">
         <is>
-          <t>-2.40%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
@@ -31658,32 +31658,32 @@
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>2.26e+05</t>
+          <t>2.24e+05</t>
         </is>
       </c>
       <c r="I74" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="J74" s="19" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="K74" s="19" t="inlineStr">
         <is>
-          <t>1.942e+06</t>
+          <t>1.957e+06</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="M74" s="19" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="N74" s="19" t="inlineStr">
@@ -31720,7 +31720,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
@@ -31755,32 +31755,32 @@
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>2.24e+05</t>
+          <t>2.33e+05</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
-          <t>1.957e+06</t>
+          <t>1.942e+06</t>
         </is>
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="M75" s="20" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
@@ -31817,7 +31817,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
@@ -31852,32 +31852,32 @@
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>2.33e+05</t>
+          <t>2.29e+05</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-6.15%</t>
         </is>
       </c>
       <c r="J76" s="19" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="K76" s="19" t="inlineStr">
         <is>
-          <t>1.942e+06</t>
+          <t>1.937e+06</t>
         </is>
       </c>
       <c r="L76" s="19" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="M76" s="19" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="N76" s="19" t="inlineStr">
@@ -31914,7 +31914,7 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
@@ -31949,32 +31949,32 @@
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>2.29e+05</t>
+          <t>2.36e+05</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>-6.15%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
-          <t>1.937e+06</t>
+          <t>1.927e+06</t>
         </is>
       </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M77" s="20" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
@@ -32011,201 +32011,201 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,548</t>
         </is>
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="D78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F78" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H78" s="19" t="inlineStr">
         <is>
-          <t>2.36e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I78" s="19" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J78" s="19" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K78" s="19" t="inlineStr">
         <is>
-          <t>1.927e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L78" s="19" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M78" s="19" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="O78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="P78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="Q78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,169</t>
         </is>
       </c>
       <c r="R78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="S78" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="22" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>158,548</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G79" s="20" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.59e+05</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="K79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.925e+06</t>
         </is>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="M79" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O79" s="20" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P79" s="20" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
-          <t>7,169</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R79" s="20" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S79" s="20" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
@@ -32240,32 +32240,32 @@
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>2.59e+05</t>
+          <t>2.33e+05</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="J80" s="19" t="inlineStr">
         <is>
-          <t>9.75%</t>
+          <t>-10.04%</t>
         </is>
       </c>
       <c r="K80" s="19" t="inlineStr">
         <is>
-          <t>1.925e+06</t>
+          <t>1.916e+06</t>
         </is>
       </c>
       <c r="L80" s="19" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="M80" s="19" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="N80" s="19" t="inlineStr">
@@ -32302,7 +32302,7 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
@@ -32337,32 +32337,32 @@
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>2.33e+05</t>
+          <t>2.19e+05</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-5.20%</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>-10.04%</t>
+          <t>-6.01%</t>
         </is>
       </c>
       <c r="K81" s="20" t="inlineStr">
         <is>
-          <t>1.916e+06</t>
+          <t>1.921e+06</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="M81" s="20" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
@@ -32399,7 +32399,7 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -32434,32 +32434,32 @@
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>2.19e+05</t>
+          <t>2.25e+05</t>
         </is>
       </c>
       <c r="I82" s="19" t="inlineStr">
         <is>
-          <t>-5.20%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="J82" s="19" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K82" s="19" t="inlineStr">
         <is>
-          <t>1.921e+06</t>
+          <t>1.929e+06</t>
         </is>
       </c>
       <c r="L82" s="19" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="M82" s="19" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="N82" s="19" t="inlineStr">
@@ -32496,22 +32496,22 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,408</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -32531,84 +32531,84 @@
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>2.25e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K83" s="20" t="inlineStr">
         <is>
-          <t>1.929e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="20" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M83" s="20" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="O83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="P83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="Q83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,170</t>
         </is>
       </c>
       <c r="R83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="S83" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>158,408</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C84" s="19" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D84" s="19" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -32628,69 +32628,69 @@
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.33e+05</t>
         </is>
       </c>
       <c r="I84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="J84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.928e+06</t>
         </is>
       </c>
       <c r="L84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="M84" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O84" s="19" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P84" s="19" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q84" s="19" t="inlineStr">
         <is>
-          <t>7,170</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R84" s="19" t="inlineStr">
         <is>
-          <t>-2.83%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S84" s="19" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
@@ -32725,32 +32725,32 @@
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>2.33e+05</t>
+          <t>2.22e+05</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="K85" s="20" t="inlineStr">
         <is>
-          <t>1.928e+06</t>
+          <t>1.947e+06</t>
         </is>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="M85" s="20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
@@ -32787,7 +32787,7 @@
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
@@ -32822,32 +32822,32 @@
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>2.31e+05</t>
         </is>
       </c>
       <c r="I86" s="19" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>5.48%</t>
         </is>
       </c>
       <c r="J86" s="19" t="inlineStr">
         <is>
-          <t>-4.72%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K86" s="19" t="inlineStr">
         <is>
-          <t>1.947e+06</t>
+          <t>1.953e+06</t>
         </is>
       </c>
       <c r="L86" s="19" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="M86" s="19" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="N86" s="19" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
@@ -32919,32 +32919,32 @@
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>2.31e+05</t>
+          <t>2.21e+05</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="K87" s="20" t="inlineStr">
         <is>
-          <t>1.953e+06</t>
+          <t>1.962e+06</t>
         </is>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="M87" s="20" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
@@ -32981,134 +32981,134 @@
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,449</t>
         </is>
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="D88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E88" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F88" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
-          <t>2.21e+05</t>
+          <t>2.28e+05</t>
         </is>
       </c>
       <c r="I88" s="19" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="J88" s="19" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K88" s="19" t="inlineStr">
         <is>
-          <t>1.962e+06</t>
+          <t>1.946e+06</t>
         </is>
       </c>
       <c r="L88" s="19" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="M88" s="19" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="P88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="Q88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,846</t>
         </is>
       </c>
       <c r="R88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-9.52%</t>
         </is>
       </c>
       <c r="S88" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.52%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="22" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>158,449</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
         <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G89" s="20" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H89" s="20" t="inlineStr">
@@ -33118,64 +33118,64 @@
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K89" s="20" t="inlineStr">
         <is>
-          <t>1.946e+06</t>
+          <t>1.949e+06</t>
         </is>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="M89" s="20" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="20" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P89" s="20" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q89" s="20" t="inlineStr">
         <is>
-          <t>6,846</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R89" s="20" t="inlineStr">
         <is>
-          <t>-9.52%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S89" s="20" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -33210,32 +33210,32 @@
       </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
-          <t>2.28e+05</t>
+          <t>2.22e+05</t>
         </is>
       </c>
       <c r="I90" s="19" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="J90" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="K90" s="19" t="inlineStr">
         <is>
-          <t>1.949e+06</t>
+          <t>1.943e+06</t>
         </is>
       </c>
       <c r="L90" s="19" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="M90" s="19" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="N90" s="19" t="inlineStr">
@@ -33272,7 +33272,7 @@
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="22" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B91" s="20" t="inlineStr">
@@ -33307,32 +33307,32 @@
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>2.22e+05</t>
+          <t>2.18e+05</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-7.63%</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="K91" s="20" t="inlineStr">
         <is>
-          <t>1.943e+06</t>
+          <t>1.932e+06</t>
         </is>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="M91" s="20" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
@@ -33369,7 +33369,7 @@
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
@@ -33404,32 +33404,32 @@
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>2.18e+05</t>
+          <t>2.16e+05</t>
         </is>
       </c>
       <c r="I92" s="19" t="inlineStr">
         <is>
-          <t>-7.63%</t>
+          <t>-16.60%</t>
         </is>
       </c>
       <c r="J92" s="19" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="K92" s="19" t="inlineStr">
         <is>
-          <t>1.932e+06</t>
+          <t>1.894e+06</t>
         </is>
       </c>
       <c r="L92" s="19" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="M92" s="19" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="N92" s="19" t="inlineStr">
@@ -33466,201 +33466,201 @@
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="22" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,432</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="G93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H93" s="20" t="inlineStr">
         <is>
-          <t>2.16e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>-16.60%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K93" s="20" t="inlineStr">
         <is>
-          <t>1.894e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L93" s="20" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="20" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="O93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="P93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,550</t>
         </is>
       </c>
       <c r="R93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-10.21%</t>
         </is>
       </c>
       <c r="S93" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.32%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>158,432</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C94" s="19" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D94" s="19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F94" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.35e+05</t>
         </is>
       </c>
       <c r="I94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="J94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="K94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.887e+06</t>
         </is>
       </c>
       <c r="L94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="M94" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O94" s="19" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P94" s="19" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q94" s="19" t="inlineStr">
         <is>
-          <t>6,550</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R94" s="19" t="inlineStr">
         <is>
-          <t>-10.21%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S94" s="19" t="inlineStr">
         <is>
-          <t>-4.32%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="22" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B95" s="20" t="inlineStr">
@@ -33695,32 +33695,32 @@
       </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>2.35e+05</t>
+          <t>2.24e+05</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>8.80%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="K95" s="20" t="inlineStr">
         <is>
-          <t>1.887e+06</t>
+          <t>1.91e+06</t>
         </is>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="M95" s="20" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -33757,7 +33757,7 @@
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
@@ -33792,32 +33792,32 @@
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>2.24e+05</t>
+          <t>2.15e+05</t>
         </is>
       </c>
       <c r="I96" s="19" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="J96" s="19" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="K96" s="19" t="inlineStr">
         <is>
-          <t>1.91e+06</t>
+          <t>1.86e+06</t>
         </is>
       </c>
       <c r="L96" s="19" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="M96" s="19" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="N96" s="19" t="inlineStr">
@@ -33854,7 +33854,7 @@
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="B97" s="20" t="inlineStr">
@@ -33889,32 +33889,32 @@
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>2.15e+05</t>
+          <t>2.03e+05</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>-4.44%</t>
+          <t>-12.88%</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-5.58%</t>
         </is>
       </c>
       <c r="K97" s="20" t="inlineStr">
         <is>
-          <t>1.86e+06</t>
+          <t>1.9e+06</t>
         </is>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="M97" s="20" t="inlineStr">
         <is>
-          <t>-2.62%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
@@ -33951,201 +33951,201 @@
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,592</t>
         </is>
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="D98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F98" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>2.03e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>-12.88%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J98" s="19" t="inlineStr">
         <is>
-          <t>-5.58%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K98" s="19" t="inlineStr">
         <is>
-          <t>1.9e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="19" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" s="19" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="O98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="P98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="Q98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,240</t>
         </is>
       </c>
       <c r="R98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="S98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10.53%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>158,592</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C99" s="20" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G99" s="20" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.07e+05</t>
         </is>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-6.76%</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.875e+06</t>
         </is>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.70%</t>
         </is>
       </c>
       <c r="M99" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O99" s="20" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P99" s="20" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q99" s="20" t="inlineStr">
         <is>
-          <t>7,240</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R99" s="20" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S99" s="20" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -34180,32 +34180,32 @@
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>2.07e+05</t>
+          <t>2.01e+05</t>
         </is>
       </c>
       <c r="I100" s="19" t="inlineStr">
         <is>
-          <t>-6.76%</t>
+          <t>-12.99%</t>
         </is>
       </c>
       <c r="J100" s="19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="K100" s="19" t="inlineStr">
         <is>
-          <t>1.875e+06</t>
+          <t>1.865e+06</t>
         </is>
       </c>
       <c r="L100" s="19" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-4.51%</t>
         </is>
       </c>
       <c r="M100" s="19" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="N100" s="19" t="inlineStr">
@@ -34242,7 +34242,7 @@
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="22" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B101" s="20" t="inlineStr">
@@ -34277,32 +34277,32 @@
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>2.01e+05</t>
+          <t>2.1e+05</t>
         </is>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>-12.99%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>-2.90%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="K101" s="20" t="inlineStr">
         <is>
-          <t>1.865e+06</t>
+          <t>1.823e+06</t>
         </is>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
-          <t>-4.51%</t>
+          <t>-7.08%</t>
         </is>
       </c>
       <c r="M101" s="20" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
@@ -34339,7 +34339,7 @@
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
@@ -34374,32 +34374,32 @@
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>2.1e+05</t>
+          <t>2.11e+05</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-7.46%</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K102" s="19" t="inlineStr">
         <is>
-          <t>1.823e+06</t>
+          <t>1.842e+06</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr">
         <is>
-          <t>-7.08%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="M102" s="19" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="N102" s="19" t="inlineStr">
@@ -34436,7 +34436,7 @@
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="22" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B103" s="20" t="inlineStr">
@@ -34471,32 +34471,32 @@
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>2.11e+05</t>
+          <t>2.3e+05</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>-7.46%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>9.01%</t>
         </is>
       </c>
       <c r="K103" s="20" t="inlineStr">
         <is>
-          <t>1.842e+06</t>
+          <t>1.859e+06</t>
         </is>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
-          <t>-5.34%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="M103" s="20" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -34533,201 +34533,201 @@
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,436</t>
         </is>
       </c>
       <c r="C104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="D104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E104" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>2.3e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I104" s="19" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J104" s="19" t="inlineStr">
         <is>
-          <t>9.01%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K104" s="19" t="inlineStr">
         <is>
-          <t>1.859e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L104" s="19" t="inlineStr">
         <is>
-          <t>-4.62%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M104" s="19" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="O104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="P104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="Q104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,922</t>
         </is>
       </c>
       <c r="R104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="S104" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.39%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>158,436</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C105" s="20" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G105" s="20" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.3e+05</t>
         </is>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.865e+06</t>
         </is>
       </c>
       <c r="L105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="M105" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O105" s="20" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P105" s="20" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
-          <t>6,922</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R105" s="20" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S105" s="20" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
@@ -34762,32 +34762,32 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>2.3e+05</t>
+          <t>2.08e+05</t>
         </is>
       </c>
       <c r="I106" s="19" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="J106" s="19" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-9.56%</t>
         </is>
       </c>
       <c r="K106" s="19" t="inlineStr">
         <is>
-          <t>1.865e+06</t>
+          <t>1.827e+06</t>
         </is>
       </c>
       <c r="L106" s="19" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="M106" s="19" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="N106" s="19" t="inlineStr">
@@ -34824,7 +34824,7 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="22" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B107" s="20" t="inlineStr">
@@ -34859,32 +34859,32 @@
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>2.08e+05</t>
+          <t>2.11e+05</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>-9.56%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K107" s="20" t="inlineStr">
         <is>
-          <t>1.827e+06</t>
+          <t>1.871e+06</t>
         </is>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>-5.43%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="M107" s="20" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -34921,7 +34921,7 @@
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
@@ -34956,32 +34956,32 @@
       </c>
       <c r="H108" s="19" t="inlineStr">
         <is>
-          <t>2.11e+05</t>
+          <t>2.14e+05</t>
         </is>
       </c>
       <c r="I108" s="19" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-8.94%</t>
         </is>
       </c>
       <c r="J108" s="19" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K108" s="19" t="inlineStr">
         <is>
-          <t>1.871e+06</t>
+          <t>1.847e+06</t>
         </is>
       </c>
       <c r="L108" s="19" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="M108" s="19" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="N108" s="19" t="inlineStr">
@@ -35018,201 +35018,201 @@
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,621</t>
         </is>
       </c>
       <c r="C109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E109" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="G109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="H109" s="20" t="inlineStr">
         <is>
-          <t>2.14e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>-8.94%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K109" s="20" t="inlineStr">
         <is>
-          <t>1.847e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L109" s="20" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M109" s="20" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="O109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="P109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="Q109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6,887</t>
         </is>
       </c>
       <c r="R109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="S109" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.51%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>158,621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D110" s="19" t="inlineStr">
         <is>
-          <t>0.12%</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F110" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.13e+05</t>
         </is>
       </c>
       <c r="I110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="J110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="K110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.851e+06</t>
         </is>
       </c>
       <c r="L110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="M110" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O110" s="19" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P110" s="19" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q110" s="19" t="inlineStr">
         <is>
-          <t>6,887</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R110" s="19" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S110" s="19" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B111" s="20" t="inlineStr">
@@ -35247,32 +35247,32 @@
       </c>
       <c r="H111" s="20" t="inlineStr">
         <is>
-          <t>2.13e+05</t>
+          <t>2.05e+05</t>
         </is>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-4.65%</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="K111" s="20" t="inlineStr">
         <is>
-          <t>1.851e+06</t>
+          <t>1.816e+06</t>
         </is>
       </c>
       <c r="L111" s="20" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="M111" s="20" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -35309,7 +35309,7 @@
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
@@ -35344,32 +35344,32 @@
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>2.05e+05</t>
+          <t>2.11e+05</t>
         </is>
       </c>
       <c r="I112" s="19" t="inlineStr">
         <is>
-          <t>-4.65%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="J112" s="19" t="inlineStr">
         <is>
-          <t>-3.76%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K112" s="19" t="inlineStr">
         <is>
-          <t>1.816e+06</t>
+          <t>1.832e+06</t>
         </is>
       </c>
       <c r="L112" s="19" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="M112" s="19" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="N112" s="19" t="inlineStr">
@@ -35406,7 +35406,7 @@
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="22" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B113" s="20" t="inlineStr">
@@ -35441,32 +35441,32 @@
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>2.11e+05</t>
+          <t>2.03e+05</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="K113" s="20" t="inlineStr">
         <is>
-          <t>1.832e+06</t>
+          <t>1.787e+06</t>
         </is>
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="M113" s="20" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>-2.46%</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -35503,201 +35503,201 @@
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>158,736</t>
         </is>
       </c>
       <c r="C114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="D114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E114" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F114" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="H114" s="19" t="inlineStr">
         <is>
-          <t>2.03e+05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I114" s="19" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J114" s="19" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K114" s="19" t="inlineStr">
         <is>
-          <t>1.787e+06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L114" s="19" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M114" s="19" t="inlineStr">
         <is>
-          <t>-2.46%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="O114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="P114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="Q114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,618</t>
         </is>
       </c>
       <c r="R114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7.33%</t>
         </is>
       </c>
       <c r="S114" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10.61%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>158,736</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C115" s="20" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E115" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F115" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G115" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.18e+05</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8.46%</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7.39%</t>
         </is>
       </c>
       <c r="K115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.809e+06</t>
         </is>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-3.00%</t>
         </is>
       </c>
       <c r="M115" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O115" s="20" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P115" s="20" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
-          <t>7,618</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R115" s="20" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S115" s="20" t="inlineStr">
         <is>
-          <t>10.61%</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
@@ -35732,32 +35732,32 @@
       </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>2.18e+05</t>
+          <t>2.08e+05</t>
         </is>
       </c>
       <c r="I116" s="19" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="J116" s="19" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="K116" s="19" t="inlineStr">
         <is>
-          <t>1.809e+06</t>
+          <t>1.808e+06</t>
         </is>
       </c>
       <c r="L116" s="19" t="inlineStr">
         <is>
-          <t>-3.00%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="M116" s="19" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="N116" s="19" t="inlineStr">
@@ -35794,7 +35794,7 @@
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="22" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B117" s="20" t="inlineStr">
@@ -35829,32 +35829,32 @@
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
-          <t>2.08e+05</t>
+          <t>2.15e+05</t>
         </is>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="K117" s="20" t="inlineStr">
         <is>
-          <t>1.808e+06</t>
+          <t>1.776e+06</t>
         </is>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="M117" s="20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
@@ -35891,7 +35891,7 @@
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
@@ -35926,32 +35926,32 @@
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>2.15e+05</t>
+          <t>1.9e+05</t>
         </is>
       </c>
       <c r="I118" s="19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>-17.39%</t>
         </is>
       </c>
       <c r="J118" s="19" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>-11.63%</t>
         </is>
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t>1.776e+06</t>
+          <t>1.758e+06</t>
         </is>
       </c>
       <c r="L118" s="19" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="M118" s="19" t="inlineStr">
         <is>
-          <t>-1.77%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="N118" s="19" t="inlineStr">
@@ -35988,7 +35988,7 @@
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B119" s="20" t="inlineStr">
@@ -36023,32 +36023,32 @@
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>1.9e+05</t>
+          <t>1.99e+05</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>-17.39%</t>
+          <t>-13.48%</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
         <is>
-          <t>-11.63%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K119" s="20" t="inlineStr">
         <is>
-          <t>1.758e+06</t>
+          <t>1.776e+06</t>
         </is>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
-          <t>-5.43%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="M119" s="20" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
@@ -36085,7 +36085,7 @@
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
@@ -36120,32 +36120,32 @@
       </c>
       <c r="H120" s="19" t="inlineStr">
         <is>
-          <t>1.99e+05</t>
+          <t>2.12e+05</t>
         </is>
       </c>
       <c r="I120" s="19" t="inlineStr">
         <is>
-          <t>-13.48%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="J120" s="19" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="K120" s="19" t="inlineStr">
         <is>
-          <t>1.776e+06</t>
+          <t>1.771e+06</t>
         </is>
       </c>
       <c r="L120" s="19" t="inlineStr">
         <is>
-          <t>-4.77%</t>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="M120" s="19" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="N120" s="19" t="inlineStr">
@@ -36182,7 +36182,7 @@
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="22" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B121" s="20" t="inlineStr">
@@ -36217,32 +36217,32 @@
       </c>
       <c r="H121" s="20" t="inlineStr">
         <is>
-          <t>2.12e+05</t>
+          <t>2.1e+05</t>
         </is>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="K121" s="20" t="inlineStr">
         <is>
-          <t>1.771e+06</t>
+          <t>1.785e+06</t>
         </is>
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="M121" s="20" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -36279,7 +36279,7 @@
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
@@ -36314,32 +36314,32 @@
       </c>
       <c r="H122" s="19" t="inlineStr">
         <is>
-          <t>2.1e+05</t>
+          <t>2.12e+05</t>
         </is>
       </c>
       <c r="I122" s="19" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="J122" s="19" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K122" s="19" t="inlineStr">
         <is>
-          <t>1.786e+06</t>
+          <t>1.777e+06</t>
         </is>
       </c>
       <c r="L122" s="19" t="inlineStr">
         <is>
-          <t>-4.54%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="M122" s="19" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="N122" s="19" t="inlineStr">
@@ -36376,7 +36376,7 @@
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="22" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B123" s="20" t="inlineStr">
@@ -36411,17 +36411,17 @@
       </c>
       <c r="H123" s="20" t="inlineStr">
         <is>
-          <t>2.15e+05</t>
+          <t>2.25e+05</t>
         </is>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="K123" s="20" t="inlineStr">
@@ -36517,7 +36517,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏦 利率與債券　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>🏦 利率與債券　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -48336,7 +48336,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>💭 信心指數　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>💭 信心指數　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -56513,7 +56513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>
@@ -59662,7 +59662,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏠 房市　歷史數據　　生成時間：2026-06-04 00:14 UTC</t>
+          <t>🏠 房市　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/excel/MacroPulse_2026-06-04.xlsx
+++ b/reports/excel/MacroPulse_2026-06-04.xlsx
@@ -651,7 +651,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>+0.530 pp</t>
+          <t>+0.370 pp</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🔥 通膨指標　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>🔥 通膨指標　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>📈 經濟成長　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>📈 經濟成長　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -24692,7 +24692,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>👷 勞動市場　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>👷 勞動市場　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36517,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏦 利率與債券　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>🏦 利率與債券　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -36658,7 +36658,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -36738,7 +36738,7 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
@@ -36748,14 +36748,14 @@
       </c>
       <c r="S4" s="19" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
@@ -36845,14 +36845,14 @@
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
@@ -36942,94 +36942,94 @@
       </c>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.930 pp</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.530 pp</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.300 pp</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.380 pp</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>-0.310 pp</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>+0.640 pp</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="Q7" s="20" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="R7" s="20" t="inlineStr">
@@ -37039,94 +37039,94 @@
       </c>
       <c r="S7" s="20" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>-0.930 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>-0.530 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>-0.300 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>-0.380 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>-0.310 pp</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>+0.640 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
@@ -37136,14 +37136,14 @@
       </c>
       <c r="S8" s="19" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -37223,7 +37223,7 @@
       </c>
       <c r="Q9" s="20" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="R9" s="20" t="inlineStr">
@@ -37233,14 +37233,14 @@
       </c>
       <c r="S9" s="20" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
@@ -37330,14 +37330,14 @@
       </c>
       <c r="S10" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R11" s="20" t="inlineStr">
@@ -37427,208 +37427,208 @@
       </c>
       <c r="S11" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.200 pp</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.200 pp</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.400 pp</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.350 pp</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.660 pp</t>
         </is>
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.430 pp</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>+0.740 pp</t>
         </is>
       </c>
       <c r="P12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>-0.640 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S12" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>-0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>-0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>-1.400 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>-0.350 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>-0.660 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>-0.430 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>+0.740 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R13" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.600 pp</t>
         </is>
       </c>
       <c r="S13" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
@@ -37708,24 +37708,24 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>-0.600 pp</t>
+          <t>-0.670 pp</t>
         </is>
       </c>
       <c r="S14" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -37805,24 +37805,24 @@
       </c>
       <c r="Q15" s="20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R15" s="20" t="inlineStr">
         <is>
-          <t>-0.670 pp</t>
+          <t>-0.770 pp</t>
         </is>
       </c>
       <c r="S15" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -37902,218 +37902,218 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>-0.770 pp</t>
+          <t>-0.870 pp</t>
         </is>
       </c>
       <c r="S16" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.500 pp</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.300 pp</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.100 pp</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.350 pp</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.700 pp</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.380 pp</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.570 pp</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.340 pp</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>+0.390 pp</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R17" s="20" t="inlineStr">
         <is>
-          <t>-0.870 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>-0.500 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>-0.300 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>-1.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>+0.350 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>-0.700 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>+0.380 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
-          <t>-0.570 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>+0.340 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>+0.390 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.770 pp</t>
         </is>
       </c>
       <c r="S18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -38193,24 +38193,24 @@
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="R19" s="20" t="inlineStr">
         <is>
-          <t>-0.770 pp</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="S19" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -38290,24 +38290,24 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S20" s="19" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -38387,24 +38387,24 @@
       </c>
       <c r="Q21" s="20" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="R21" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="S21" s="20" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -38484,218 +38484,218 @@
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>+0.250 pp</t>
         </is>
       </c>
       <c r="S22" s="19" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>+0.180 pp</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.290 pp</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>+0.480 pp</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
       <c r="Q23" s="20" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R23" s="20" t="inlineStr">
         <is>
-          <t>+0.250 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S23" s="20" t="inlineStr">
         <is>
-          <t>+0.180 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>+0.290 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="inlineStr">
-        <is>
-          <t>+0.480 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P24" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -38775,24 +38775,24 @@
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="R25" s="20" t="inlineStr">
         <is>
-          <t>+0.300 pp</t>
+          <t>+0.320 pp</t>
         </is>
       </c>
       <c r="S25" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -38872,24 +38872,24 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>+0.320 pp</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S26" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -38969,218 +38969,218 @@
       </c>
       <c r="Q27" s="20" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R27" s="20" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.460 pp</t>
         </is>
       </c>
       <c r="S27" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.850 pp</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.230 pp</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.370 pp</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="L28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.440 pp</t>
         </is>
       </c>
       <c r="M28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>+0.610 pp</t>
         </is>
       </c>
       <c r="P28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="Q28" s="19" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R28" s="19" t="inlineStr">
         <is>
-          <t>+0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>-0.850 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>-0.230 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>+0.370 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>+0.440 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="O29" s="13" t="inlineStr">
-        <is>
-          <t>+0.610 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P29" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q29" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="R29" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S29" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -39260,24 +39260,24 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.510 pp</t>
         </is>
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -39357,24 +39357,24 @@
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R31" s="20" t="inlineStr">
         <is>
-          <t>+0.510 pp</t>
+          <t>+0.640 pp</t>
         </is>
       </c>
       <c r="S31" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -39454,218 +39454,218 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>+0.640 pp</t>
+          <t>+0.730 pp</t>
         </is>
       </c>
       <c r="S32" s="19" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.570 pp</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.590 pp</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.270 pp</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>+0.620 pp</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R33" s="20" t="inlineStr">
         <is>
-          <t>+0.730 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S33" s="20" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>+0.570 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>6.91</t>
+        </is>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
           <t>+0.590 pp</t>
         </is>
       </c>
-      <c r="M34" s="19" t="inlineStr">
-        <is>
-          <t>+0.270 pp</t>
-        </is>
-      </c>
-      <c r="N34" s="19" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="O34" s="13" t="inlineStr">
-        <is>
-          <t>+0.620 pp</t>
-        </is>
-      </c>
-      <c r="P34" s="19" t="inlineStr">
-        <is>
-          <t>+0.190 pp</t>
-        </is>
-      </c>
-      <c r="Q34" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R34" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S34" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -39745,24 +39745,24 @@
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="R35" s="20" t="inlineStr">
         <is>
-          <t>+0.590 pp</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S35" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -39842,24 +39842,24 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.500 pp</t>
         </is>
       </c>
       <c r="S36" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -39939,24 +39939,24 @@
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="R37" s="20" t="inlineStr">
         <is>
-          <t>+0.500 pp</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="S37" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -40036,218 +40036,218 @@
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="S38" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.330 pp</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="K39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>+0.580 pp</t>
         </is>
       </c>
       <c r="P39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R39" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S39" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>-0.330 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q40" s="19" t="inlineStr">
+        <is>
+          <t>6.89</t>
+        </is>
+      </c>
+      <c r="R40" s="19" t="inlineStr">
+        <is>
+          <t>+0.110 pp</t>
+        </is>
+      </c>
+      <c r="S40" s="19" t="inlineStr">
+        <is>
           <t>-0.060 pp</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>+0.240 pp</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>-0.180 pp</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="inlineStr">
-        <is>
-          <t>-0.170 pp</t>
-        </is>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="O40" s="13" t="inlineStr">
-        <is>
-          <t>+0.580 pp</t>
-        </is>
-      </c>
-      <c r="P40" s="19" t="inlineStr">
-        <is>
-          <t>-0.120 pp</t>
-        </is>
-      </c>
-      <c r="Q40" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R40" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S40" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -40327,24 +40327,24 @@
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="R41" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="S41" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -40424,12 +40424,12 @@
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="S42" s="19" t="inlineStr">
@@ -40441,7 +40441,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -40521,218 +40521,218 @@
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="R43" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="S43" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.240 pp</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="L44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O44" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>+0.690 pp</t>
         </is>
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R44" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S44" s="19" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
-          <t>-0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
         <is>
-          <t>-0.170 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M45" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="O45" s="13" t="inlineStr">
-        <is>
-          <t>+0.690 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P45" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="R45" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="S45" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -40812,24 +40812,24 @@
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
       <c r="S46" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -40909,12 +40909,12 @@
       </c>
       <c r="Q47" s="20" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="R47" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="S47" s="20" t="inlineStr">
@@ -40926,7 +40926,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
@@ -41006,218 +41006,218 @@
       </c>
       <c r="Q48" s="19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="R48" s="19" t="inlineStr">
         <is>
-          <t>-0.180 pp</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="S48" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.090 pp</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="J49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="K49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="L49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="M49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O49" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O49" s="13" t="inlineStr">
+        <is>
+          <t>+0.830 pp</t>
         </is>
       </c>
       <c r="P49" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R49" s="20" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S49" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>-1.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O50" s="13" t="inlineStr">
-        <is>
-          <t>+0.830 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O50" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q50" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="R50" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.290 pp</t>
         </is>
       </c>
       <c r="S50" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -41297,24 +41297,24 @@
       </c>
       <c r="Q51" s="20" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="R51" s="20" t="inlineStr">
         <is>
-          <t>-0.290 pp</t>
+          <t>-0.420 pp</t>
         </is>
       </c>
       <c r="S51" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -41394,24 +41394,24 @@
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>-0.420 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S52" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>+0.210 pp</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -41491,218 +41491,218 @@
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R53" s="20" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="S53" s="20" t="inlineStr">
         <is>
-          <t>+0.210 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.940 pp</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="K54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="L54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.280 pp</t>
         </is>
       </c>
       <c r="M54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O54" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O54" s="13" t="inlineStr">
+        <is>
+          <t>+0.870 pp</t>
         </is>
       </c>
       <c r="P54" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="Q54" s="19" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="R54" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S54" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P55" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q55" s="20" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="R55" s="20" t="inlineStr">
+        <is>
+          <t>-0.110 pp</t>
+        </is>
+      </c>
+      <c r="S55" s="20" t="inlineStr">
+        <is>
           <t>+0.000 pp</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>-0.940 pp</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>+0.140 pp</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
-        <is>
-          <t>-0.060 pp</t>
-        </is>
-      </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>+0.140 pp</t>
-        </is>
-      </c>
-      <c r="K55" s="20" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>+0.280 pp</t>
-        </is>
-      </c>
-      <c r="M55" s="20" t="inlineStr">
-        <is>
-          <t>+0.190 pp</t>
-        </is>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O55" s="13" t="inlineStr">
-        <is>
-          <t>+0.870 pp</t>
-        </is>
-      </c>
-      <c r="P55" s="20" t="inlineStr">
-        <is>
-          <t>+0.000 pp</t>
-        </is>
-      </c>
-      <c r="Q55" s="20" t="inlineStr">
-        <is>
-          <t>6.76</t>
-        </is>
-      </c>
-      <c r="R55" s="20" t="inlineStr">
-        <is>
-          <t>-0.130 pp</t>
-        </is>
-      </c>
-      <c r="S55" s="20" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
@@ -41782,24 +41782,24 @@
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="S56" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -41879,12 +41879,12 @@
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="R57" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="S57" s="20" t="inlineStr">
@@ -41896,7 +41896,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -41976,218 +41976,218 @@
       </c>
       <c r="Q58" s="19" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="R58" s="19" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="S58" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.850 pp</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.450 pp</t>
         </is>
       </c>
       <c r="M59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O59" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="O59" s="13" t="inlineStr">
+        <is>
+          <t>+0.920 pp</t>
         </is>
       </c>
       <c r="P59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q59" s="20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R59" s="20" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S59" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
-          <t>-0.850 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I60" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J60" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q60" s="19" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="R60" s="19" t="inlineStr">
+        <is>
+          <t>+0.200 pp</t>
+        </is>
+      </c>
+      <c r="S60" s="19" t="inlineStr">
+        <is>
           <t>-0.040 pp</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="L60" s="19" t="inlineStr">
-        <is>
-          <t>+0.450 pp</t>
-        </is>
-      </c>
-      <c r="M60" s="19" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
-        </is>
-      </c>
-      <c r="N60" s="19" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="O60" s="13" t="inlineStr">
-        <is>
-          <t>+0.920 pp</t>
-        </is>
-      </c>
-      <c r="P60" s="19" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
-        </is>
-      </c>
-      <c r="Q60" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R60" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S60" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -42267,24 +42267,24 @@
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="R61" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>+0.170 pp</t>
         </is>
       </c>
       <c r="S61" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
@@ -42364,24 +42364,24 @@
       </c>
       <c r="Q62" s="19" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R62" s="19" t="inlineStr">
         <is>
-          <t>+0.170 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="S62" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -42461,218 +42461,218 @@
       </c>
       <c r="Q63" s="20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="R63" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="S63" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
       <c r="K64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="L64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.460 pp</t>
         </is>
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O64" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O64" s="13" t="inlineStr">
+        <is>
+          <t>+0.760 pp</t>
         </is>
       </c>
       <c r="P64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="Q64" s="19" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R64" s="19" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S64" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H65" s="20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>+0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J65" s="20" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L65" s="20" t="inlineStr">
         <is>
-          <t>+0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M65" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="O65" s="13" t="inlineStr">
-        <is>
-          <t>+0.760 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P65" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q65" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="R65" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="S65" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -42752,24 +42752,24 @@
       </c>
       <c r="Q66" s="19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R66" s="19" t="inlineStr">
         <is>
+          <t>-0.110 pp</t>
+        </is>
+      </c>
+      <c r="S66" s="19" t="inlineStr">
+        <is>
           <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="S66" s="19" t="inlineStr">
-        <is>
-          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
@@ -42849,24 +42849,24 @@
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="R67" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="S67" s="20" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="23" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -42946,24 +42946,24 @@
       </c>
       <c r="Q68" s="19" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="R68" s="19" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
       <c r="S68" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
@@ -43043,218 +43043,218 @@
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R69" s="20" t="inlineStr">
         <is>
+          <t>-0.040 pp</t>
+        </is>
+      </c>
+      <c r="S69" s="20" t="inlineStr">
+        <is>
           <t>-0.020 pp</t>
-        </is>
-      </c>
-      <c r="S69" s="20" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.390 pp</t>
         </is>
       </c>
       <c r="J70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="K70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="L70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.720 pp</t>
         </is>
       </c>
       <c r="M70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O70" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O70" s="13" t="inlineStr">
+        <is>
+          <t>+0.650 pp</t>
         </is>
       </c>
       <c r="P70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="Q70" s="19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R70" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S70" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P71" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q71" s="20" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="R71" s="20" t="inlineStr">
+        <is>
           <t>-0.180 pp</t>
         </is>
       </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
-        <is>
-          <t>+0.390 pp</t>
-        </is>
-      </c>
-      <c r="J71" s="20" t="inlineStr">
-        <is>
-          <t>-0.130 pp</t>
-        </is>
-      </c>
-      <c r="K71" s="20" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="L71" s="20" t="inlineStr">
-        <is>
-          <t>+0.720 pp</t>
-        </is>
-      </c>
-      <c r="M71" s="20" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
-        </is>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="O71" s="13" t="inlineStr">
-        <is>
-          <t>+0.650 pp</t>
-        </is>
-      </c>
-      <c r="P71" s="20" t="inlineStr">
-        <is>
-          <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="Q71" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R71" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S71" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
@@ -43334,24 +43334,24 @@
       </c>
       <c r="Q72" s="19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="R72" s="19" t="inlineStr">
         <is>
-          <t>-0.180 pp</t>
+          <t>-0.280 pp</t>
         </is>
       </c>
       <c r="S72" s="19" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
@@ -43436,19 +43436,19 @@
       </c>
       <c r="R73" s="20" t="inlineStr">
         <is>
-          <t>-0.280 pp</t>
+          <t>-0.310 pp</t>
         </is>
       </c>
       <c r="S73" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
@@ -43528,218 +43528,218 @@
       </c>
       <c r="Q74" s="19" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="R74" s="19" t="inlineStr">
         <is>
-          <t>-0.310 pp</t>
+          <t>-0.290 pp</t>
         </is>
       </c>
       <c r="S74" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.910 pp</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.700 pp</t>
         </is>
       </c>
       <c r="M75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O75" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t>+0.450 pp</t>
         </is>
       </c>
       <c r="P75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q75" s="20" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R75" s="20" t="inlineStr">
         <is>
-          <t>-0.290 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S75" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>-0.910 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J76" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K76" s="19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="19" t="inlineStr">
         <is>
-          <t>+0.700 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="O76" s="9" t="inlineStr">
-        <is>
-          <t>+0.450 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O76" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P76" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q76" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="R76" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S76" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
@@ -43819,24 +43819,24 @@
       </c>
       <c r="Q77" s="20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R77" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.460 pp</t>
         </is>
       </c>
       <c r="S77" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
@@ -43916,24 +43916,24 @@
       </c>
       <c r="Q78" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="R78" s="19" t="inlineStr">
         <is>
-          <t>-0.460 pp</t>
+          <t>-0.510 pp</t>
         </is>
       </c>
       <c r="S78" s="19" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
@@ -44013,218 +44013,218 @@
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R79" s="20" t="inlineStr">
         <is>
-          <t>-0.510 pp</t>
+          <t>-0.370 pp</t>
         </is>
       </c>
       <c r="S79" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.740 pp</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="J80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="K80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="L80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="M80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O80" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>+0.420 pp</t>
         </is>
       </c>
       <c r="P80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q80" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R80" s="19" t="inlineStr">
         <is>
-          <t>-0.370 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S80" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>-0.740 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G81" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K81" s="20" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M81" s="20" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="O81" s="9" t="inlineStr">
-        <is>
-          <t>+0.420 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O81" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P81" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="R81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.380 pp</t>
         </is>
       </c>
       <c r="S81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -44304,24 +44304,24 @@
       </c>
       <c r="Q82" s="19" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R82" s="19" t="inlineStr">
         <is>
-          <t>-0.380 pp</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="S82" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
@@ -44401,24 +44401,24 @@
       </c>
       <c r="Q83" s="20" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="R83" s="20" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>-0.470 pp</t>
         </is>
       </c>
       <c r="S83" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
@@ -44498,24 +44498,24 @@
       </c>
       <c r="Q84" s="19" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="R84" s="19" t="inlineStr">
         <is>
-          <t>-0.470 pp</t>
+          <t>-0.530 pp</t>
         </is>
       </c>
       <c r="S84" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
@@ -44595,218 +44595,218 @@
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="R85" s="20" t="inlineStr">
         <is>
-          <t>-0.530 pp</t>
+          <t>-0.460 pp</t>
         </is>
       </c>
       <c r="S85" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="C86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.760 pp</t>
         </is>
       </c>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.210 pp</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.710 pp</t>
         </is>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="J86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="K86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="L86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="M86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O86" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="inlineStr">
+        <is>
+          <t>+0.440 pp</t>
         </is>
       </c>
       <c r="P86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="Q86" s="19" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R86" s="19" t="inlineStr">
         <is>
-          <t>-0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S86" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>-0.760 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>-0.210 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>-0.710 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G87" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K87" s="20" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M87" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="O87" s="9" t="inlineStr">
-        <is>
-          <t>+0.440 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O87" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P87" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q87" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R87" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.360 pp</t>
         </is>
       </c>
       <c r="S87" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
@@ -44886,24 +44886,24 @@
       </c>
       <c r="Q88" s="19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="R88" s="19" t="inlineStr">
         <is>
-          <t>-0.360 pp</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S88" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B89" s="20" t="inlineStr">
@@ -44983,12 +44983,12 @@
       </c>
       <c r="Q89" s="20" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="R89" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.300 pp</t>
         </is>
       </c>
       <c r="S89" s="20" t="inlineStr">
@@ -45000,7 +45000,7 @@
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -45080,218 +45080,218 @@
       </c>
       <c r="Q90" s="19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="R90" s="19" t="inlineStr">
         <is>
-          <t>-0.300 pp</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="S90" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.760 pp</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.730 pp</t>
         </is>
       </c>
       <c r="G91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.250 pp</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="K91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.220 pp</t>
         </is>
       </c>
       <c r="M91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O91" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
+        <is>
+          <t>+0.470 pp</t>
         </is>
       </c>
       <c r="P91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="Q91" s="20" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R91" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S91" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>-0.760 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D92" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q92" s="19" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="R92" s="19" t="inlineStr">
+        <is>
           <t>-0.160 pp</t>
         </is>
       </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F92" s="19" t="inlineStr">
-        <is>
-          <t>-0.730 pp</t>
-        </is>
-      </c>
-      <c r="G92" s="19" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
-        </is>
-      </c>
-      <c r="H92" s="19" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="I92" s="19" t="inlineStr">
-        <is>
-          <t>-0.250 pp</t>
-        </is>
-      </c>
-      <c r="J92" s="19" t="inlineStr">
-        <is>
-          <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="K92" s="19" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="L92" s="19" t="inlineStr">
-        <is>
-          <t>+0.220 pp</t>
-        </is>
-      </c>
-      <c r="M92" s="19" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
-        </is>
-      </c>
-      <c r="N92" s="19" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="O92" s="9" t="inlineStr">
-        <is>
-          <t>+0.470 pp</t>
-        </is>
-      </c>
-      <c r="P92" s="19" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
-        </is>
-      </c>
-      <c r="Q92" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R92" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S92" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B93" s="20" t="inlineStr">
@@ -45371,24 +45371,24 @@
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R93" s="20" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="S93" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
@@ -45468,24 +45468,24 @@
       </c>
       <c r="Q94" s="19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="R94" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
       <c r="S94" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B95" s="20" t="inlineStr">
@@ -45565,24 +45565,24 @@
       </c>
       <c r="Q95" s="20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="R95" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="S95" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
@@ -45662,12 +45662,12 @@
       </c>
       <c r="Q96" s="19" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="R96" s="19" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="S96" s="19" t="inlineStr">
@@ -45679,201 +45679,201 @@
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.730 pp</t>
         </is>
       </c>
       <c r="G97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.420 pp</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="K97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="M97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O97" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>+0.320 pp</t>
         </is>
       </c>
       <c r="P97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R97" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S97" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D98" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>-0.730 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>-0.420 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J98" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K98" s="19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="O98" s="9" t="inlineStr">
-        <is>
-          <t>+0.320 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O98" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P98" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="R98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="S98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B99" s="20" t="inlineStr">
@@ -45953,24 +45953,24 @@
       </c>
       <c r="Q99" s="20" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="R99" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S99" s="20" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="23" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -46050,24 +46050,24 @@
       </c>
       <c r="Q100" s="19" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="S100" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B101" s="20" t="inlineStr">
@@ -46147,218 +46147,218 @@
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="R101" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="S101" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.740 pp</t>
         </is>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.320 pp</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="K102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
       <c r="M102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O102" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="O102" s="9" t="inlineStr">
+        <is>
+          <t>+0.410 pp</t>
         </is>
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S102" s="19" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C103" s="20" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
         <is>
-          <t>-0.740 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G103" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>-0.320 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K103" s="20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M103" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="O103" s="9" t="inlineStr">
-        <is>
-          <t>+0.410 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O103" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P103" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q103" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="R103" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S103" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
@@ -46438,24 +46438,24 @@
       </c>
       <c r="Q104" s="19" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R104" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="S104" s="19" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="23" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B105" s="20" t="inlineStr">
@@ -46535,24 +46535,24 @@
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="R105" s="20" t="inlineStr">
         <is>
-          <t>-0.170 pp</t>
+          <t>-0.220 pp</t>
         </is>
       </c>
       <c r="S105" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
@@ -46632,218 +46632,218 @@
       </c>
       <c r="Q106" s="19" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="R106" s="19" t="inlineStr">
         <is>
-          <t>-0.220 pp</t>
+          <t>-0.210 pp</t>
         </is>
       </c>
       <c r="S106" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
       <c r="K107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.250 pp</t>
         </is>
       </c>
       <c r="M107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.090 pp</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O107" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O107" s="9" t="inlineStr">
+        <is>
+          <t>+0.220 pp</t>
         </is>
       </c>
       <c r="P107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R107" s="20" t="inlineStr">
         <is>
-          <t>-0.210 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S107" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D108" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I108" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J108" s="19" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K108" s="19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L108" s="19" t="inlineStr">
         <is>
-          <t>+0.250 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M108" s="19" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="O108" s="9" t="inlineStr">
-        <is>
-          <t>+0.220 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O108" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P108" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q108" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R108" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.220 pp</t>
         </is>
       </c>
       <c r="S108" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B109" s="20" t="inlineStr">
@@ -46923,24 +46923,24 @@
       </c>
       <c r="Q109" s="20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="R109" s="20" t="inlineStr">
         <is>
-          <t>-0.220 pp</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="S109" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
@@ -47020,12 +47020,12 @@
       </c>
       <c r="Q110" s="19" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R110" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="S110" s="19" t="inlineStr">
@@ -47037,7 +47037,7 @@
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B111" s="20" t="inlineStr">
@@ -47117,218 +47117,218 @@
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="R111" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.230 pp</t>
         </is>
       </c>
       <c r="S111" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.090 pp</t>
         </is>
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="J112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="K112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="L112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="M112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O112" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="O112" s="9" t="inlineStr">
+        <is>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="P112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q112" s="19" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R112" s="19" t="inlineStr">
         <is>
-          <t>+0.230 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S112" s="19" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C113" s="20" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K113" s="20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M113" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="O113" s="9" t="inlineStr">
-        <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O113" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P113" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="R113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="S113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
@@ -47408,24 +47408,24 @@
       </c>
       <c r="Q114" s="19" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="R114" s="19" t="inlineStr">
         <is>
-          <t>+0.300 pp</t>
+          <t>+0.310 pp</t>
         </is>
       </c>
       <c r="S114" s="19" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B115" s="20" t="inlineStr">
@@ -47505,24 +47505,24 @@
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R115" s="20" t="inlineStr">
         <is>
-          <t>+0.310 pp</t>
+          <t>+0.210 pp</t>
         </is>
       </c>
       <c r="S115" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
@@ -47602,12 +47602,12 @@
       </c>
       <c r="Q116" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="R116" s="19" t="inlineStr">
         <is>
-          <t>+0.210 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="S116" s="19" t="inlineStr">
@@ -47619,7 +47619,7 @@
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B117" s="20" t="inlineStr">
@@ -47699,24 +47699,24 @@
       </c>
       <c r="Q117" s="20" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R117" s="20" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="S117" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
@@ -47736,84 +47736,84 @@
       </c>
       <c r="E118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
       <c r="G118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="J118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.170 pp</t>
         </is>
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="L118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="M118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O118" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="O118" s="6" t="inlineStr">
+        <is>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="P118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="Q118" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R118" s="19" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S118" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B119" s="20" t="inlineStr">
@@ -47833,84 +47833,84 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G119" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P119" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q119" s="20" t="inlineStr">
+        <is>
+          <t>6.37</t>
+        </is>
+      </c>
+      <c r="R119" s="20" t="inlineStr">
+        <is>
+          <t>+0.280 pp</t>
+        </is>
+      </c>
+      <c r="S119" s="20" t="inlineStr">
+        <is>
           <t>+0.070 pp</t>
-        </is>
-      </c>
-      <c r="J119" s="20" t="inlineStr">
-        <is>
-          <t>+0.170 pp</t>
-        </is>
-      </c>
-      <c r="K119" s="20" t="inlineStr">
-        <is>
-          <t>5.04</t>
-        </is>
-      </c>
-      <c r="L119" s="20" t="inlineStr">
-        <is>
-          <t>+0.140 pp</t>
-        </is>
-      </c>
-      <c r="M119" s="20" t="inlineStr">
-        <is>
-          <t>+0.130 pp</t>
-        </is>
-      </c>
-      <c r="N119" s="20" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="O119" s="6" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
-        </is>
-      </c>
-      <c r="P119" s="20" t="inlineStr">
-        <is>
-          <t>-0.030 pp</t>
-        </is>
-      </c>
-      <c r="Q119" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R119" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S119" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
@@ -47990,24 +47990,24 @@
       </c>
       <c r="Q120" s="19" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="R120" s="19" t="inlineStr">
         <is>
-          <t>+0.280 pp</t>
+          <t>+0.350 pp</t>
         </is>
       </c>
       <c r="S120" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B121" s="20" t="inlineStr">
@@ -48087,24 +48087,24 @@
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="R121" s="20" t="inlineStr">
         <is>
-          <t>+0.350 pp</t>
+          <t>+0.530 pp</t>
         </is>
       </c>
       <c r="S121" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>+0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
@@ -48184,7 +48184,7 @@
       </c>
       <c r="Q122" s="19" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="R122" s="19" t="inlineStr">
@@ -48194,14 +48194,14 @@
       </c>
       <c r="S122" s="19" t="inlineStr">
         <is>
-          <t>+0.150 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B123" s="20" t="inlineStr">
@@ -48281,17 +48281,17 @@
       </c>
       <c r="Q123" s="20" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="R123" s="20" t="inlineStr">
         <is>
-          <t>+0.530 pp</t>
+          <t>+0.370 pp</t>
         </is>
       </c>
       <c r="S123" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
@@ -48336,7 +48336,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>💭 信心指數　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>💭 信心指數　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -56513,7 +56513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -59662,7 +59662,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏠 房市　歷史數據　　生成時間：2026-06-04 15:58 UTC</t>
+          <t>🏠 房市　歷史數據　　生成時間：2026-06-04 23:46 UTC</t>
         </is>
       </c>
     </row>
